--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5684-2026 artfynd.xlsx
+++ b/artfynd/A 5684-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136541236</v>
       </c>
       <c r="B2" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
